--- a/RocioCordoba/02_ObispoSalguero387_13C/MesesPagados_ObispoSalguero387_13C.xlsx
+++ b/RocioCordoba/02_ObispoSalguero387_13C/MesesPagados_ObispoSalguero387_13C.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\00_ENGITHUB\Modulo02_JavaScript\RocioCordoba\02_ObispoSalguero387_13C\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3482F021-7342-455E-B7E7-037545D106C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD81F89C-CA70-4111-B1D7-9484F2D1EA58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
   <si>
     <t>AÑO</t>
   </si>
@@ -46,6 +46,21 @@
   </si>
   <si>
     <t>TOTAL</t>
+  </si>
+  <si>
+    <t>Alquiler</t>
+  </si>
+  <si>
+    <t>Importe</t>
+  </si>
+  <si>
+    <t>Concepto</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Cada uno</t>
   </si>
 </sst>
 </file>
@@ -72,7 +87,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -82,6 +97,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA3DBFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -98,11 +119,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -383,7 +405,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C3:K8"/>
+  <dimension ref="C3:K22"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="5" max="5" width="12.28515625" bestFit="1" customWidth="1"/>
@@ -515,7 +537,50 @@
         <v>889842.47</v>
       </c>
     </row>
+    <row r="16" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="F16" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G17" s="1">
+        <v>748951</v>
+      </c>
+    </row>
+    <row r="18" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F18" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G18" s="1">
+        <v>140891.47</v>
+      </c>
+    </row>
+    <row r="20" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F20" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G20" s="1">
+        <f>+G17+G18</f>
+        <v>889842.47</v>
+      </c>
+    </row>
+    <row r="22" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F22" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G22" s="1">
+        <f>+G20/2</f>
+        <v>444921.23499999999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/RocioCordoba/02_ObispoSalguero387_13C/MesesPagados_ObispoSalguero387_13C.xlsx
+++ b/RocioCordoba/02_ObispoSalguero387_13C/MesesPagados_ObispoSalguero387_13C.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\00_ENGITHUB\Modulo02_JavaScript\RocioCordoba\02_ObispoSalguero387_13C\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Daniel M\Desktop\Modulo02_JavaScript\RocioCordoba\02_ObispoSalguero387_13C\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3482F021-7342-455E-B7E7-037545D106C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -51,7 +50,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;\ #,##0.00"/>
   </numFmts>
@@ -382,8 +381,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C3:K8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="C3:K11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="5" max="5" width="12.28515625" bestFit="1" customWidth="1"/>
@@ -515,6 +514,12 @@
         <v>889842.47</v>
       </c>
     </row>
+    <row r="11" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="F11" s="1">
+        <f>+F8+G7</f>
+        <v>797902</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/RocioCordoba/02_ObispoSalguero387_13C/MesesPagados_ObispoSalguero387_13C.xlsx
+++ b/RocioCordoba/02_ObispoSalguero387_13C/MesesPagados_ObispoSalguero387_13C.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\00_ENGITHUB\Modulo02_JavaScript\RocioCordoba\02_ObispoSalguero387_13C\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD81F89C-CA70-4111-B1D7-9484F2D1EA58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{685E3EB2-0093-43F1-8EB2-156A4737A9A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -537,6 +537,28 @@
         <v>889842.47</v>
       </c>
     </row>
+    <row r="9" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C9">
+        <v>2026</v>
+      </c>
+      <c r="D9">
+        <v>7</v>
+      </c>
+      <c r="E9" s="1">
+        <v>748951</v>
+      </c>
+      <c r="F9" s="1">
+        <f>+E9</f>
+        <v>748951</v>
+      </c>
+      <c r="I9" s="1">
+        <v>139957.26</v>
+      </c>
+      <c r="K9" s="1">
+        <f>+E9+I9</f>
+        <v>888908.26</v>
+      </c>
+    </row>
     <row r="16" spans="3:11" x14ac:dyDescent="0.25">
       <c r="F16" s="4" t="s">
         <v>9</v>
@@ -558,7 +580,7 @@
         <v>5</v>
       </c>
       <c r="G18" s="1">
-        <v>140891.47</v>
+        <v>139957.26</v>
       </c>
     </row>
     <row r="20" spans="6:7" x14ac:dyDescent="0.25">
@@ -567,7 +589,7 @@
       </c>
       <c r="G20" s="1">
         <f>+G17+G18</f>
-        <v>889842.47</v>
+        <v>888908.26</v>
       </c>
     </row>
     <row r="22" spans="6:7" x14ac:dyDescent="0.25">
@@ -576,7 +598,7 @@
       </c>
       <c r="G22" s="1">
         <f>+G20/2</f>
-        <v>444921.23499999999</v>
+        <v>444454.13</v>
       </c>
     </row>
   </sheetData>
